--- a/data/compare_data/default_action13/episode_0_results_20250720_185238.xlsx
+++ b/data/compare_data/default_action13/episode_0_results_20250720_185238.xlsx
@@ -4,10 +4,11 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13380"/>
+    <workbookView windowWidth="29868" windowHeight="13380" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="26">
   <si>
     <t>year</t>
   </si>
@@ -100,6 +101,12 @@
   <si>
     <t/>
   </si>
+  <si>
+    <t>all</t>
+  </si>
+  <si>
+    <t>E11</t>
+  </si>
 </sst>
 </file>
 
@@ -111,7 +118,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -122,13 +129,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -596,28 +596,31 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -626,118 +629,115 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2131,6 +2131,11 @@
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext uri="{0b15fc19-7d7d-44ad-8c2d-2c3a37ce22c3}">
+        <chartProps xmlns="https://web.wps.cn/et/2018/main" chartId="{fbeb64b9-7d53-44b7-8ffc-c52968cb8b7e}"/>
+      </c:ext>
+    </c:extLst>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2950,6 +2955,11 @@
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext uri="{0b15fc19-7d7d-44ad-8c2d-2c3a37ce22c3}">
+        <chartProps xmlns="https://web.wps.cn/et/2018/main" chartId="{cbd0e4f7-1a7d-4dec-92ce-a731dabe38be}"/>
+      </c:ext>
+    </c:extLst>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -10395,4 +10405,2293 @@
   <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:I85"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="9"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="9" max="9" width="14.1111111111111"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2">
+        <v>2017</v>
+      </c>
+      <c r="B2">
+        <v>613.478105046222</v>
+      </c>
+      <c r="C2">
+        <v>22.0132657300889</v>
+      </c>
+      <c r="D2">
+        <v>8.59896237378051</v>
+      </c>
+      <c r="E2">
+        <v>13.3995188800066</v>
+      </c>
+      <c r="F2">
+        <v>47.5073850879936</v>
+      </c>
+      <c r="G2">
+        <v>50.312</v>
+      </c>
+      <c r="I2">
+        <f>B2-C2-D2-E2-F2-G2</f>
+        <v>471.646972974352</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3">
+        <v>2018</v>
+      </c>
+      <c r="B3">
+        <v>616.74633870264</v>
+      </c>
+      <c r="C3">
+        <v>28.1879621497637</v>
+      </c>
+      <c r="D3">
+        <v>14.80584270986</v>
+      </c>
+      <c r="E3">
+        <v>13.3995188800066</v>
+      </c>
+      <c r="F3">
+        <v>47.5073850879936</v>
+      </c>
+      <c r="G3">
+        <v>50.312</v>
+      </c>
+      <c r="I3">
+        <f t="shared" ref="I3:I34" si="0">B3-C3-D3-E3-F3-G3</f>
+        <v>462.533629875016</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4">
+        <v>2019</v>
+      </c>
+      <c r="B4">
+        <v>619.942605065637</v>
+      </c>
+      <c r="C4">
+        <v>34.2404988579844</v>
+      </c>
+      <c r="D4">
+        <v>20.9938050064355</v>
+      </c>
+      <c r="E4">
+        <v>13.3995188800066</v>
+      </c>
+      <c r="F4">
+        <v>47.5073850879936</v>
+      </c>
+      <c r="G4">
+        <v>50.312</v>
+      </c>
+      <c r="I4">
+        <f t="shared" si="0"/>
+        <v>453.489397233217</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5">
+        <v>2020</v>
+      </c>
+      <c r="B5">
+        <v>622.272707564947</v>
+      </c>
+      <c r="C5">
+        <v>40.3112767676637</v>
+      </c>
+      <c r="D5">
+        <v>27.2293681782088</v>
+      </c>
+      <c r="E5">
+        <v>13.3995188800066</v>
+      </c>
+      <c r="F5">
+        <v>47.5073850879936</v>
+      </c>
+      <c r="G5">
+        <v>50.312</v>
+      </c>
+      <c r="I5">
+        <f t="shared" si="0"/>
+        <v>443.513158651074</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6">
+        <v>2021</v>
+      </c>
+      <c r="B6">
+        <v>641.296814330282</v>
+      </c>
+      <c r="C6">
+        <v>46.2628529650499</v>
+      </c>
+      <c r="D6">
+        <v>33.4629852007899</v>
+      </c>
+      <c r="E6">
+        <v>13.3995188800066</v>
+      </c>
+      <c r="F6">
+        <v>47.5073850879936</v>
+      </c>
+      <c r="G6">
+        <v>50.312</v>
+      </c>
+      <c r="I6">
+        <f t="shared" si="0"/>
+        <v>450.352072196442</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7">
+        <v>2022</v>
+      </c>
+      <c r="B7">
+        <v>657.82361241711</v>
+      </c>
+      <c r="C7">
+        <v>52.2810153013936</v>
+      </c>
+      <c r="D7">
+        <v>39.8515849510934</v>
+      </c>
+      <c r="E7">
+        <v>13.3995188800066</v>
+      </c>
+      <c r="F7">
+        <v>47.5073850879936</v>
+      </c>
+      <c r="G7">
+        <v>50.312</v>
+      </c>
+      <c r="I7">
+        <f t="shared" si="0"/>
+        <v>454.472108196623</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8">
+        <v>2023</v>
+      </c>
+      <c r="B8">
+        <v>672.443263257573</v>
+      </c>
+      <c r="C8">
+        <v>58.2608356151491</v>
+      </c>
+      <c r="D8">
+        <v>46.3359309555519</v>
+      </c>
+      <c r="E8">
+        <v>13.3995188800066</v>
+      </c>
+      <c r="F8">
+        <v>47.5073850879936</v>
+      </c>
+      <c r="G8">
+        <v>50.312</v>
+      </c>
+      <c r="I8">
+        <f t="shared" si="0"/>
+        <v>456.627592718872</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9">
+        <v>2024</v>
+      </c>
+      <c r="B9">
+        <v>685.225237050332</v>
+      </c>
+      <c r="C9">
+        <v>64.2484239609608</v>
+      </c>
+      <c r="D9">
+        <v>52.8892758192312</v>
+      </c>
+      <c r="E9">
+        <v>13.3995188800066</v>
+      </c>
+      <c r="F9">
+        <v>47.5073850879936</v>
+      </c>
+      <c r="G9">
+        <v>50.312</v>
+      </c>
+      <c r="I9">
+        <f t="shared" si="0"/>
+        <v>456.86863330214</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10">
+        <v>2025</v>
+      </c>
+      <c r="B10">
+        <v>696.889194926988</v>
+      </c>
+      <c r="C10">
+        <v>70.8442897327333</v>
+      </c>
+      <c r="D10">
+        <v>59.4814911958225</v>
+      </c>
+      <c r="E10">
+        <v>13.3995188800066</v>
+      </c>
+      <c r="F10">
+        <v>47.5073850879936</v>
+      </c>
+      <c r="G10">
+        <v>50.312</v>
+      </c>
+      <c r="I10">
+        <f t="shared" si="0"/>
+        <v>455.344510030432</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11">
+        <v>2026</v>
+      </c>
+      <c r="B11">
+        <v>705.559807951731</v>
+      </c>
+      <c r="C11">
+        <v>78.2867828960483</v>
+      </c>
+      <c r="D11">
+        <v>66.1575179583348</v>
+      </c>
+      <c r="E11">
+        <v>13.3995188800066</v>
+      </c>
+      <c r="F11">
+        <v>47.5073850879936</v>
+      </c>
+      <c r="G11">
+        <v>50.312</v>
+      </c>
+      <c r="I11">
+        <f t="shared" si="0"/>
+        <v>449.896603129348</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12">
+        <v>2027</v>
+      </c>
+      <c r="B12">
+        <v>714.26625081222</v>
+      </c>
+      <c r="C12">
+        <v>86.799537729003</v>
+      </c>
+      <c r="D12">
+        <v>72.7515166108014</v>
+      </c>
+      <c r="E12">
+        <v>13.3995188800066</v>
+      </c>
+      <c r="F12">
+        <v>47.5073850879936</v>
+      </c>
+      <c r="G12">
+        <v>50.312</v>
+      </c>
+      <c r="I12">
+        <f t="shared" si="0"/>
+        <v>443.496292504415</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13">
+        <v>2028</v>
+      </c>
+      <c r="B13">
+        <v>721.819464470292</v>
+      </c>
+      <c r="C13">
+        <v>96.4546649291145</v>
+      </c>
+      <c r="D13">
+        <v>79.3148065452735</v>
+      </c>
+      <c r="E13">
+        <v>13.3995188800066</v>
+      </c>
+      <c r="F13">
+        <v>47.5073850879936</v>
+      </c>
+      <c r="G13">
+        <v>50.312</v>
+      </c>
+      <c r="I13">
+        <f t="shared" si="0"/>
+        <v>434.831089027904</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14">
+        <v>2029</v>
+      </c>
+      <c r="B14">
+        <v>726.891222906976</v>
+      </c>
+      <c r="C14">
+        <v>107.284274457181</v>
+      </c>
+      <c r="D14">
+        <v>85.8628380064053</v>
+      </c>
+      <c r="E14">
+        <v>13.3995188800066</v>
+      </c>
+      <c r="F14">
+        <v>47.5073850879936</v>
+      </c>
+      <c r="G14">
+        <v>50.312</v>
+      </c>
+      <c r="I14">
+        <f t="shared" si="0"/>
+        <v>422.525206475389</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15">
+        <v>2030</v>
+      </c>
+      <c r="B15">
+        <v>730.273244803459</v>
+      </c>
+      <c r="C15">
+        <v>119.392705931305</v>
+      </c>
+      <c r="D15">
+        <v>92.3202428520395</v>
+      </c>
+      <c r="E15">
+        <v>13.3995188800066</v>
+      </c>
+      <c r="F15">
+        <v>47.5073850879936</v>
+      </c>
+      <c r="G15">
+        <v>50.312</v>
+      </c>
+      <c r="I15">
+        <f t="shared" si="0"/>
+        <v>407.341392052114</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16">
+        <v>2031</v>
+      </c>
+      <c r="B16">
+        <v>746.654996560707</v>
+      </c>
+      <c r="C16">
+        <v>132.963400271474</v>
+      </c>
+      <c r="D16">
+        <v>98.5808131760138</v>
+      </c>
+      <c r="E16">
+        <v>13.3995188800066</v>
+      </c>
+      <c r="F16">
+        <v>47.5073850879936</v>
+      </c>
+      <c r="G16">
+        <v>50.312</v>
+      </c>
+      <c r="I16">
+        <f t="shared" si="0"/>
+        <v>403.891879145219</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17">
+        <v>2032</v>
+      </c>
+      <c r="B17">
+        <v>759.44140800352</v>
+      </c>
+      <c r="C17">
+        <v>147.980469605381</v>
+      </c>
+      <c r="D17">
+        <v>104.885076390204</v>
+      </c>
+      <c r="E17">
+        <v>13.3995188800066</v>
+      </c>
+      <c r="F17">
+        <v>47.5073850879936</v>
+      </c>
+      <c r="G17">
+        <v>50.312</v>
+      </c>
+      <c r="I17">
+        <f t="shared" si="0"/>
+        <v>395.356958039935</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18">
+        <v>2033</v>
+      </c>
+      <c r="B18">
+        <v>772.048976730478</v>
+      </c>
+      <c r="C18">
+        <v>164.663780849091</v>
+      </c>
+      <c r="D18">
+        <v>111.028297224325</v>
+      </c>
+      <c r="E18">
+        <v>13.3995188800066</v>
+      </c>
+      <c r="F18">
+        <v>47.5073850879936</v>
+      </c>
+      <c r="G18">
+        <v>50.312</v>
+      </c>
+      <c r="I18">
+        <f t="shared" si="0"/>
+        <v>385.137994689062</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19">
+        <v>2034</v>
+      </c>
+      <c r="B19">
+        <v>781.095136076297</v>
+      </c>
+      <c r="C19">
+        <v>182.796030754682</v>
+      </c>
+      <c r="D19">
+        <v>117.16181057296</v>
+      </c>
+      <c r="E19">
+        <v>13.3995188800066</v>
+      </c>
+      <c r="F19">
+        <v>47.5073850879936</v>
+      </c>
+      <c r="G19">
+        <v>50.312</v>
+      </c>
+      <c r="I19">
+        <f t="shared" si="0"/>
+        <v>369.918390780655</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20">
+        <v>2035</v>
+      </c>
+      <c r="B20">
+        <v>789.884490522081</v>
+      </c>
+      <c r="C20">
+        <v>202.488738513117</v>
+      </c>
+      <c r="D20">
+        <v>123.414645559257</v>
+      </c>
+      <c r="E20">
+        <v>13.3995188800066</v>
+      </c>
+      <c r="F20">
+        <v>47.5073850879936</v>
+      </c>
+      <c r="G20">
+        <v>50.312</v>
+      </c>
+      <c r="I20">
+        <f t="shared" si="0"/>
+        <v>352.762202481707</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21">
+        <v>2036</v>
+      </c>
+      <c r="B21">
+        <v>796.801921772626</v>
+      </c>
+      <c r="C21">
+        <v>223.518319610312</v>
+      </c>
+      <c r="D21">
+        <v>129.95802025357</v>
+      </c>
+      <c r="E21">
+        <v>13.3995188800066</v>
+      </c>
+      <c r="F21">
+        <v>47.5073850879936</v>
+      </c>
+      <c r="G21">
+        <v>50.312</v>
+      </c>
+      <c r="I21">
+        <f t="shared" si="0"/>
+        <v>332.106677940744</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22">
+        <v>2037</v>
+      </c>
+      <c r="B22">
+        <v>802.569411398285</v>
+      </c>
+      <c r="C22">
+        <v>245.696427586816</v>
+      </c>
+      <c r="D22">
+        <v>136.756019267356</v>
+      </c>
+      <c r="E22">
+        <v>13.3995188800066</v>
+      </c>
+      <c r="F22">
+        <v>47.5073850879936</v>
+      </c>
+      <c r="G22">
+        <v>50.312</v>
+      </c>
+      <c r="I22">
+        <f t="shared" si="0"/>
+        <v>308.898060576113</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23">
+        <v>2038</v>
+      </c>
+      <c r="B23">
+        <v>806.849845447232</v>
+      </c>
+      <c r="C23">
+        <v>268.703716050465</v>
+      </c>
+      <c r="D23">
+        <v>143.756681309947</v>
+      </c>
+      <c r="E23">
+        <v>13.3995188800066</v>
+      </c>
+      <c r="F23">
+        <v>47.5073850879936</v>
+      </c>
+      <c r="G23">
+        <v>50.312</v>
+      </c>
+      <c r="I23">
+        <f t="shared" si="0"/>
+        <v>283.17054411882</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24">
+        <v>2039</v>
+      </c>
+      <c r="B24">
+        <v>809.97818224745</v>
+      </c>
+      <c r="C24">
+        <v>292.178904133717</v>
+      </c>
+      <c r="D24">
+        <v>150.887518491511</v>
+      </c>
+      <c r="E24">
+        <v>13.3995188800066</v>
+      </c>
+      <c r="F24">
+        <v>47.5073850879936</v>
+      </c>
+      <c r="G24">
+        <v>50.312</v>
+      </c>
+      <c r="I24">
+        <f t="shared" si="0"/>
+        <v>255.692855654222</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25">
+        <v>2040</v>
+      </c>
+      <c r="B25">
+        <v>811.924879857842</v>
+      </c>
+      <c r="C25">
+        <v>315.694704937427</v>
+      </c>
+      <c r="D25">
+        <v>158.059024060744</v>
+      </c>
+      <c r="E25">
+        <v>13.3995188800066</v>
+      </c>
+      <c r="F25">
+        <v>47.5073850879936</v>
+      </c>
+      <c r="G25">
+        <v>50.312</v>
+      </c>
+      <c r="I25">
+        <f t="shared" si="0"/>
+        <v>226.952246891671</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26">
+        <v>2041</v>
+      </c>
+      <c r="B26">
+        <v>842.353493750593</v>
+      </c>
+      <c r="C26">
+        <v>338.996008931346</v>
+      </c>
+      <c r="D26">
+        <v>165.217472836359</v>
+      </c>
+      <c r="E26">
+        <v>13.3995188800066</v>
+      </c>
+      <c r="F26">
+        <v>47.5073850879936</v>
+      </c>
+      <c r="G26">
+        <v>50.312</v>
+      </c>
+      <c r="I26">
+        <f t="shared" si="0"/>
+        <v>226.921108014888</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27">
+        <v>2042</v>
+      </c>
+      <c r="B27">
+        <v>854.744059532923</v>
+      </c>
+      <c r="C27">
+        <v>362.803904434486</v>
+      </c>
+      <c r="D27">
+        <v>172.604461694993</v>
+      </c>
+      <c r="E27">
+        <v>13.3995188800066</v>
+      </c>
+      <c r="F27">
+        <v>47.5073850879936</v>
+      </c>
+      <c r="G27">
+        <v>50.312</v>
+      </c>
+      <c r="I27">
+        <f t="shared" si="0"/>
+        <v>208.116789435444</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28">
+        <v>2043</v>
+      </c>
+      <c r="B28">
+        <v>866.916653324723</v>
+      </c>
+      <c r="C28">
+        <v>386.133969521382</v>
+      </c>
+      <c r="D28">
+        <v>179.924832951792</v>
+      </c>
+      <c r="E28">
+        <v>13.3995188800066</v>
+      </c>
+      <c r="F28">
+        <v>47.5073850879936</v>
+      </c>
+      <c r="G28">
+        <v>50.312</v>
+      </c>
+      <c r="I28">
+        <f t="shared" si="0"/>
+        <v>189.638946883549</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29">
+        <v>2044</v>
+      </c>
+      <c r="B29">
+        <v>878.269569059</v>
+      </c>
+      <c r="C29">
+        <v>408.74961496612</v>
+      </c>
+      <c r="D29">
+        <v>187.12045817881</v>
+      </c>
+      <c r="E29">
+        <v>13.3995188800066</v>
+      </c>
+      <c r="F29">
+        <v>47.5073850879936</v>
+      </c>
+      <c r="G29">
+        <v>50.312</v>
+      </c>
+      <c r="I29">
+        <f t="shared" si="0"/>
+        <v>171.18059194607</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="A30">
+        <v>2045</v>
+      </c>
+      <c r="B30">
+        <v>888.706490098357</v>
+      </c>
+      <c r="C30">
+        <v>430.394621865718</v>
+      </c>
+      <c r="D30">
+        <v>194.111795903296</v>
+      </c>
+      <c r="E30">
+        <v>13.3995188800066</v>
+      </c>
+      <c r="F30">
+        <v>47.5073850879936</v>
+      </c>
+      <c r="G30">
+        <v>50.312</v>
+      </c>
+      <c r="I30">
+        <f t="shared" si="0"/>
+        <v>152.981168361343</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31">
+        <v>2046</v>
+      </c>
+      <c r="B31">
+        <v>898.58521428269</v>
+      </c>
+      <c r="C31">
+        <v>450.887489788217</v>
+      </c>
+      <c r="D31">
+        <v>200.804827569058</v>
+      </c>
+      <c r="E31">
+        <v>13.3995188800066</v>
+      </c>
+      <c r="F31">
+        <v>47.5073850879936</v>
+      </c>
+      <c r="G31">
+        <v>50.312</v>
+      </c>
+      <c r="I31">
+        <f t="shared" si="0"/>
+        <v>135.673992957415</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="A32">
+        <v>2047</v>
+      </c>
+      <c r="B32">
+        <v>908.482380141782</v>
+      </c>
+      <c r="C32">
+        <v>470.171153274022</v>
+      </c>
+      <c r="D32">
+        <v>207.126027501754</v>
+      </c>
+      <c r="E32">
+        <v>13.3995188800066</v>
+      </c>
+      <c r="F32">
+        <v>47.5073850879936</v>
+      </c>
+      <c r="G32">
+        <v>50.312</v>
+      </c>
+      <c r="I32">
+        <f t="shared" si="0"/>
+        <v>119.966295398006</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
+      <c r="A33">
+        <v>2048</v>
+      </c>
+      <c r="B33">
+        <v>916.711466826135</v>
+      </c>
+      <c r="C33">
+        <v>488.089457326489</v>
+      </c>
+      <c r="D33">
+        <v>213.092858426672</v>
+      </c>
+      <c r="E33">
+        <v>13.3995188800066</v>
+      </c>
+      <c r="F33">
+        <v>47.5073850879936</v>
+      </c>
+      <c r="G33">
+        <v>50.312</v>
+      </c>
+      <c r="I33">
+        <f t="shared" si="0"/>
+        <v>104.310247104974</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
+      <c r="A34">
+        <v>2049</v>
+      </c>
+      <c r="B34">
+        <v>924.756153733442</v>
+      </c>
+      <c r="C34">
+        <v>504.576546977868</v>
+      </c>
+      <c r="D34">
+        <v>218.561408521415</v>
+      </c>
+      <c r="E34">
+        <v>13.3995188800066</v>
+      </c>
+      <c r="F34">
+        <v>47.5073850879936</v>
+      </c>
+      <c r="G34">
+        <v>50.312</v>
+      </c>
+      <c r="I34">
+        <f t="shared" si="0"/>
+        <v>90.3992942661588</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
+      <c r="A35">
+        <v>2050</v>
+      </c>
+      <c r="B35">
+        <v>932.046937872819</v>
+      </c>
+      <c r="C35">
+        <v>519.651014596722</v>
+      </c>
+      <c r="D35">
+        <v>223.545179137248</v>
+      </c>
+      <c r="E35">
+        <v>13.3995188800066</v>
+      </c>
+      <c r="F35">
+        <v>47.5073850879936</v>
+      </c>
+      <c r="G35">
+        <v>50.312</v>
+      </c>
+      <c r="I35">
+        <f t="shared" ref="I35:I66" si="1">B35-C35-D35-E35-F35-G35</f>
+        <v>77.6318401708487</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
+      <c r="A36">
+        <v>2051</v>
+      </c>
+      <c r="B36">
+        <v>941.198283556208</v>
+      </c>
+      <c r="C36">
+        <v>533.366288717765</v>
+      </c>
+      <c r="D36">
+        <v>228.017036186395</v>
+      </c>
+      <c r="E36">
+        <v>13.3995188800066</v>
+      </c>
+      <c r="F36">
+        <v>47.5073850879936</v>
+      </c>
+      <c r="G36">
+        <v>50.312</v>
+      </c>
+      <c r="I36">
+        <f t="shared" si="1"/>
+        <v>68.5960546840479</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
+      <c r="A37">
+        <v>2052</v>
+      </c>
+      <c r="B37">
+        <v>949.573511381232</v>
+      </c>
+      <c r="C37">
+        <v>545.97140011342</v>
+      </c>
+      <c r="D37">
+        <v>232.088943874422</v>
+      </c>
+      <c r="E37">
+        <v>13.3995188800066</v>
+      </c>
+      <c r="F37">
+        <v>47.5073850879936</v>
+      </c>
+      <c r="G37">
+        <v>50.312</v>
+      </c>
+      <c r="I37">
+        <f t="shared" si="1"/>
+        <v>60.2942634253898</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
+      <c r="A38">
+        <v>2053</v>
+      </c>
+      <c r="B38">
+        <v>957.524705383313</v>
+      </c>
+      <c r="C38">
+        <v>557.525913097091</v>
+      </c>
+      <c r="D38">
+        <v>235.748680780048</v>
+      </c>
+      <c r="E38">
+        <v>13.3995188800066</v>
+      </c>
+      <c r="F38">
+        <v>47.5073850879936</v>
+      </c>
+      <c r="G38">
+        <v>50.312</v>
+      </c>
+      <c r="I38">
+        <f t="shared" si="1"/>
+        <v>53.0312075381737</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9">
+      <c r="A39">
+        <v>2054</v>
+      </c>
+      <c r="B39">
+        <v>964.879623936478</v>
+      </c>
+      <c r="C39">
+        <v>568.107444530614</v>
+      </c>
+      <c r="D39">
+        <v>239.034039015488</v>
+      </c>
+      <c r="E39">
+        <v>13.3995188800066</v>
+      </c>
+      <c r="F39">
+        <v>47.5073850879936</v>
+      </c>
+      <c r="G39">
+        <v>50.312</v>
+      </c>
+      <c r="I39">
+        <f t="shared" si="1"/>
+        <v>46.5192364223758</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9">
+      <c r="A40">
+        <v>2055</v>
+      </c>
+      <c r="B40">
+        <v>971.755075890993</v>
+      </c>
+      <c r="C40">
+        <v>577.783672866221</v>
+      </c>
+      <c r="D40">
+        <v>241.960235628275</v>
+      </c>
+      <c r="E40">
+        <v>13.3995188800066</v>
+      </c>
+      <c r="F40">
+        <v>47.5073850879936</v>
+      </c>
+      <c r="G40">
+        <v>50.312</v>
+      </c>
+      <c r="I40">
+        <f t="shared" si="1"/>
+        <v>40.7922634284968</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9">
+      <c r="A41">
+        <v>2056</v>
+      </c>
+      <c r="B41">
+        <v>979.60603109984</v>
+      </c>
+      <c r="C41">
+        <v>586.778198365104</v>
+      </c>
+      <c r="D41">
+        <v>244.560250264773</v>
+      </c>
+      <c r="E41">
+        <v>13.3995188800066</v>
+      </c>
+      <c r="F41">
+        <v>47.5073850879936</v>
+      </c>
+      <c r="G41">
+        <v>50.312</v>
+      </c>
+      <c r="I41">
+        <f t="shared" si="1"/>
+        <v>37.0486785019628</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9">
+      <c r="A42">
+        <v>2057</v>
+      </c>
+      <c r="B42">
+        <v>985.031463445641</v>
+      </c>
+      <c r="C42">
+        <v>595.069878526993</v>
+      </c>
+      <c r="D42">
+        <v>247.001966533004</v>
+      </c>
+      <c r="E42">
+        <v>13.3995188800066</v>
+      </c>
+      <c r="F42">
+        <v>47.5073850879936</v>
+      </c>
+      <c r="G42">
+        <v>50.312</v>
+      </c>
+      <c r="I42">
+        <f t="shared" si="1"/>
+        <v>31.7407144176438</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9">
+      <c r="A43">
+        <v>2058</v>
+      </c>
+      <c r="B43">
+        <v>995.74502798724</v>
+      </c>
+      <c r="C43">
+        <v>602.672632168323</v>
+      </c>
+      <c r="D43">
+        <v>249.133232497399</v>
+      </c>
+      <c r="E43">
+        <v>13.3995188800066</v>
+      </c>
+      <c r="F43">
+        <v>47.5073850879936</v>
+      </c>
+      <c r="G43">
+        <v>50.312</v>
+      </c>
+      <c r="I43">
+        <f t="shared" si="1"/>
+        <v>32.7202593535177</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9">
+      <c r="A44">
+        <v>2059</v>
+      </c>
+      <c r="B44">
+        <v>1008.457682909</v>
+      </c>
+      <c r="C44">
+        <v>610.067292460926</v>
+      </c>
+      <c r="D44">
+        <v>251.322278032442</v>
+      </c>
+      <c r="E44">
+        <v>13.3995188800066</v>
+      </c>
+      <c r="F44">
+        <v>47.5073850879936</v>
+      </c>
+      <c r="G44">
+        <v>50.312</v>
+      </c>
+      <c r="I44">
+        <f t="shared" si="1"/>
+        <v>35.8492084476319</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9">
+      <c r="A45">
+        <v>2060</v>
+      </c>
+      <c r="B45">
+        <v>1020.776782443</v>
+      </c>
+      <c r="C45">
+        <v>617.499777663703</v>
+      </c>
+      <c r="D45">
+        <v>253.632229040907</v>
+      </c>
+      <c r="E45">
+        <v>13.3995188800066</v>
+      </c>
+      <c r="F45">
+        <v>47.5073850879936</v>
+      </c>
+      <c r="G45">
+        <v>50.312</v>
+      </c>
+      <c r="I45">
+        <f t="shared" si="1"/>
+        <v>38.4258717703898</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9">
+      <c r="A46">
+        <v>2061</v>
+      </c>
+      <c r="B46">
+        <v>1035.62828515567</v>
+      </c>
+      <c r="C46">
+        <v>624.971287198024</v>
+      </c>
+      <c r="D46">
+        <v>256.057377286557</v>
+      </c>
+      <c r="E46">
+        <v>13.3995188800066</v>
+      </c>
+      <c r="F46">
+        <v>47.5073850879936</v>
+      </c>
+      <c r="G46">
+        <v>50.312</v>
+      </c>
+      <c r="I46">
+        <f t="shared" si="1"/>
+        <v>43.3807167030888</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9">
+      <c r="A47">
+        <v>2062</v>
+      </c>
+      <c r="B47">
+        <v>1050.04972270919</v>
+      </c>
+      <c r="C47">
+        <v>633.176549613272</v>
+      </c>
+      <c r="D47">
+        <v>258.876026281129</v>
+      </c>
+      <c r="E47">
+        <v>13.3995188800066</v>
+      </c>
+      <c r="F47">
+        <v>47.5073850879936</v>
+      </c>
+      <c r="G47">
+        <v>50.312</v>
+      </c>
+      <c r="I47">
+        <f t="shared" si="1"/>
+        <v>46.7782428467889</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9">
+      <c r="A48">
+        <v>2063</v>
+      </c>
+      <c r="B48">
+        <v>1063.9546283772</v>
+      </c>
+      <c r="C48">
+        <v>641.130290598262</v>
+      </c>
+      <c r="D48">
+        <v>261.827085740495</v>
+      </c>
+      <c r="E48">
+        <v>13.3995188800066</v>
+      </c>
+      <c r="F48">
+        <v>47.5073850879936</v>
+      </c>
+      <c r="G48">
+        <v>50.312</v>
+      </c>
+      <c r="I48">
+        <f t="shared" si="1"/>
+        <v>49.7783480704427</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9">
+      <c r="A49">
+        <v>2064</v>
+      </c>
+      <c r="B49">
+        <v>1077.51681005149</v>
+      </c>
+      <c r="C49">
+        <v>649.354167539363</v>
+      </c>
+      <c r="D49">
+        <v>264.877370896604</v>
+      </c>
+      <c r="E49">
+        <v>13.3995188800066</v>
+      </c>
+      <c r="F49">
+        <v>47.5073850879936</v>
+      </c>
+      <c r="G49">
+        <v>50.312</v>
+      </c>
+      <c r="I49">
+        <f t="shared" si="1"/>
+        <v>52.0663676475228</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9">
+      <c r="A50">
+        <v>2065</v>
+      </c>
+      <c r="B50">
+        <v>1090.62085831868</v>
+      </c>
+      <c r="C50">
+        <v>657.79490529816</v>
+      </c>
+      <c r="D50">
+        <v>268.130982734612</v>
+      </c>
+      <c r="E50">
+        <v>13.3995188800066</v>
+      </c>
+      <c r="F50">
+        <v>47.5073850879936</v>
+      </c>
+      <c r="G50">
+        <v>50.312</v>
+      </c>
+      <c r="I50">
+        <f t="shared" si="1"/>
+        <v>53.4760663179077</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9">
+      <c r="A51">
+        <v>2066</v>
+      </c>
+      <c r="B51">
+        <v>1103.28308861526</v>
+      </c>
+      <c r="C51">
+        <v>665.914060408091</v>
+      </c>
+      <c r="D51">
+        <v>271.396046801045</v>
+      </c>
+      <c r="E51">
+        <v>13.3995188800066</v>
+      </c>
+      <c r="F51">
+        <v>47.5073850879936</v>
+      </c>
+      <c r="G51">
+        <v>50.312</v>
+      </c>
+      <c r="I51">
+        <f t="shared" si="1"/>
+        <v>54.7540774381239</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9">
+      <c r="A52">
+        <v>2067</v>
+      </c>
+      <c r="B52">
+        <v>1115.63554644159</v>
+      </c>
+      <c r="C52">
+        <v>674.144912941401</v>
+      </c>
+      <c r="D52">
+        <v>274.694266009817</v>
+      </c>
+      <c r="E52">
+        <v>13.3995188800066</v>
+      </c>
+      <c r="F52">
+        <v>47.5073850879936</v>
+      </c>
+      <c r="G52">
+        <v>50.312</v>
+      </c>
+      <c r="I52">
+        <f t="shared" si="1"/>
+        <v>55.5774635223717</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9">
+      <c r="A53">
+        <v>2068</v>
+      </c>
+      <c r="B53">
+        <v>1127.5144014311</v>
+      </c>
+      <c r="C53">
+        <v>682.183068487707</v>
+      </c>
+      <c r="D53">
+        <v>278.057410129887</v>
+      </c>
+      <c r="E53">
+        <v>13.3995188800066</v>
+      </c>
+      <c r="F53">
+        <v>47.5073850879936</v>
+      </c>
+      <c r="G53">
+        <v>50.312</v>
+      </c>
+      <c r="I53">
+        <f t="shared" si="1"/>
+        <v>56.0550188455057</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9">
+      <c r="A54">
+        <v>2069</v>
+      </c>
+      <c r="B54">
+        <v>1139.11233929394</v>
+      </c>
+      <c r="C54">
+        <v>690.257239140223</v>
+      </c>
+      <c r="D54">
+        <v>281.410228602957</v>
+      </c>
+      <c r="E54">
+        <v>13.3995188800066</v>
+      </c>
+      <c r="F54">
+        <v>47.5073850879936</v>
+      </c>
+      <c r="G54">
+        <v>50.312</v>
+      </c>
+      <c r="I54">
+        <f t="shared" si="1"/>
+        <v>56.2259675827599</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9">
+      <c r="A55">
+        <v>2070</v>
+      </c>
+      <c r="B55">
+        <v>1150.26386189633</v>
+      </c>
+      <c r="C55">
+        <v>698.132087391853</v>
+      </c>
+      <c r="D55">
+        <v>284.79879040819</v>
+      </c>
+      <c r="E55">
+        <v>13.3995188800066</v>
+      </c>
+      <c r="F55">
+        <v>47.5073850879936</v>
+      </c>
+      <c r="G55">
+        <v>50.312</v>
+      </c>
+      <c r="I55">
+        <f t="shared" si="1"/>
+        <v>56.1140801282867</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9">
+      <c r="A56">
+        <v>2071</v>
+      </c>
+      <c r="B56">
+        <v>1162.48481814928</v>
+      </c>
+      <c r="C56">
+        <v>705.974475479206</v>
+      </c>
+      <c r="D56">
+        <v>288.165820691336</v>
+      </c>
+      <c r="E56">
+        <v>13.3995188800066</v>
+      </c>
+      <c r="F56">
+        <v>47.5073850879936</v>
+      </c>
+      <c r="G56">
+        <v>50.312</v>
+      </c>
+      <c r="I56">
+        <f t="shared" si="1"/>
+        <v>57.1256180107378</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9">
+      <c r="A57">
+        <v>2072</v>
+      </c>
+      <c r="B57">
+        <v>1174.24242692279</v>
+      </c>
+      <c r="C57">
+        <v>713.677959269251</v>
+      </c>
+      <c r="D57">
+        <v>291.581136922448</v>
+      </c>
+      <c r="E57">
+        <v>13.3995188800066</v>
+      </c>
+      <c r="F57">
+        <v>47.5073850879936</v>
+      </c>
+      <c r="G57">
+        <v>50.312</v>
+      </c>
+      <c r="I57">
+        <f t="shared" si="1"/>
+        <v>57.7644267630907</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9">
+      <c r="A58">
+        <v>2073</v>
+      </c>
+      <c r="B58">
+        <v>1185.71408441561</v>
+      </c>
+      <c r="C58">
+        <v>721.419430513973</v>
+      </c>
+      <c r="D58">
+        <v>294.98853242523</v>
+      </c>
+      <c r="E58">
+        <v>13.3995188800066</v>
+      </c>
+      <c r="F58">
+        <v>47.5073850879936</v>
+      </c>
+      <c r="G58">
+        <v>50.312</v>
+      </c>
+      <c r="I58">
+        <f t="shared" si="1"/>
+        <v>58.0872175084067</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9">
+      <c r="A59">
+        <v>2074</v>
+      </c>
+      <c r="B59">
+        <v>1196.74559231832</v>
+      </c>
+      <c r="C59">
+        <v>729.010652372785</v>
+      </c>
+      <c r="D59">
+        <v>298.424215812078</v>
+      </c>
+      <c r="E59">
+        <v>13.3995188800066</v>
+      </c>
+      <c r="F59">
+        <v>47.5073850879936</v>
+      </c>
+      <c r="G59">
+        <v>50.312</v>
+      </c>
+      <c r="I59">
+        <f t="shared" si="1"/>
+        <v>58.0918201654568</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9">
+      <c r="A60">
+        <v>2075</v>
+      </c>
+      <c r="B60">
+        <v>1207.4908558902</v>
+      </c>
+      <c r="C60">
+        <v>736.578278237653</v>
+      </c>
+      <c r="D60">
+        <v>301.834260297932</v>
+      </c>
+      <c r="E60">
+        <v>13.3995188800066</v>
+      </c>
+      <c r="F60">
+        <v>47.5073850879936</v>
+      </c>
+      <c r="G60">
+        <v>50.312</v>
+      </c>
+      <c r="I60">
+        <f t="shared" si="1"/>
+        <v>57.8594133866148</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9">
+      <c r="A61">
+        <v>2076</v>
+      </c>
+      <c r="B61">
+        <v>1217.82707806915</v>
+      </c>
+      <c r="C61">
+        <v>743.992187790317</v>
+      </c>
+      <c r="D61">
+        <v>305.248453166218</v>
+      </c>
+      <c r="E61">
+        <v>13.3995188800066</v>
+      </c>
+      <c r="F61">
+        <v>47.5073850879936</v>
+      </c>
+      <c r="G61">
+        <v>50.312</v>
+      </c>
+      <c r="I61">
+        <f t="shared" si="1"/>
+        <v>57.3675331446149</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9">
+      <c r="A62">
+        <v>2077</v>
+      </c>
+      <c r="B62">
+        <v>1227.86591993307</v>
+      </c>
+      <c r="C62">
+        <v>751.318366126014</v>
+      </c>
+      <c r="D62">
+        <v>308.621549568956</v>
+      </c>
+      <c r="E62">
+        <v>13.3995188800066</v>
+      </c>
+      <c r="F62">
+        <v>47.5073850879936</v>
+      </c>
+      <c r="G62">
+        <v>50.312</v>
+      </c>
+      <c r="I62">
+        <f t="shared" si="1"/>
+        <v>56.7071002700998</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9">
+      <c r="A63">
+        <v>2078</v>
+      </c>
+      <c r="B63">
+        <v>1237.66159816616</v>
+      </c>
+      <c r="C63">
+        <v>758.490006076833</v>
+      </c>
+      <c r="D63">
+        <v>311.971869251733</v>
+      </c>
+      <c r="E63">
+        <v>13.3995188800066</v>
+      </c>
+      <c r="F63">
+        <v>47.5073850879936</v>
+      </c>
+      <c r="G63">
+        <v>50.312</v>
+      </c>
+      <c r="I63">
+        <f t="shared" si="1"/>
+        <v>55.9808188695939</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9">
+      <c r="A64">
+        <v>2079</v>
+      </c>
+      <c r="B64">
+        <v>1247.14909207505</v>
+      </c>
+      <c r="C64">
+        <v>765.541106776117</v>
+      </c>
+      <c r="D64">
+        <v>315.276550157535</v>
+      </c>
+      <c r="E64">
+        <v>13.3995188800066</v>
+      </c>
+      <c r="F64">
+        <v>47.5073850879936</v>
+      </c>
+      <c r="G64">
+        <v>50.312</v>
+      </c>
+      <c r="I64">
+        <f t="shared" si="1"/>
+        <v>55.1125311733979</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9">
+      <c r="A65">
+        <v>2080</v>
+      </c>
+      <c r="B65">
+        <v>1256.32603739826</v>
+      </c>
+      <c r="C65">
+        <v>772.439924820725</v>
+      </c>
+      <c r="D65">
+        <v>318.540531562603</v>
+      </c>
+      <c r="E65">
+        <v>13.3995188800066</v>
+      </c>
+      <c r="F65">
+        <v>47.5073850879936</v>
+      </c>
+      <c r="G65">
+        <v>50.312</v>
+      </c>
+      <c r="I65">
+        <f t="shared" si="1"/>
+        <v>54.1266770469319</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9">
+      <c r="A66">
+        <v>2081</v>
+      </c>
+      <c r="B66">
+        <v>1266.29362483401</v>
+      </c>
+      <c r="C66">
+        <v>779.210083149014</v>
+      </c>
+      <c r="D66">
+        <v>321.759201723957</v>
+      </c>
+      <c r="E66">
+        <v>13.3995188800066</v>
+      </c>
+      <c r="F66">
+        <v>47.5073850879936</v>
+      </c>
+      <c r="G66">
+        <v>50.312</v>
+      </c>
+      <c r="I66">
+        <f t="shared" si="1"/>
+        <v>54.1054359930387</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9">
+      <c r="A67">
+        <v>2082</v>
+      </c>
+      <c r="B67">
+        <v>1275.93115477675</v>
+      </c>
+      <c r="C67">
+        <v>785.912175506966</v>
+      </c>
+      <c r="D67">
+        <v>324.974294312067</v>
+      </c>
+      <c r="E67">
+        <v>13.3995188800066</v>
+      </c>
+      <c r="F67">
+        <v>47.5073850879936</v>
+      </c>
+      <c r="G67">
+        <v>50.312</v>
+      </c>
+      <c r="I67">
+        <f t="shared" ref="I67:I84" si="2">B67-C67-D67-E67-F67-G67</f>
+        <v>53.8257809897167</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9">
+      <c r="A68">
+        <v>2083</v>
+      </c>
+      <c r="B68">
+        <v>1285.2428076198</v>
+      </c>
+      <c r="C68">
+        <v>792.540294935857</v>
+      </c>
+      <c r="D68">
+        <v>328.168906746333</v>
+      </c>
+      <c r="E68">
+        <v>13.3995188800066</v>
+      </c>
+      <c r="F68">
+        <v>47.5073850879936</v>
+      </c>
+      <c r="G68">
+        <v>50.312</v>
+      </c>
+      <c r="I68">
+        <f t="shared" si="2"/>
+        <v>53.3147019696098</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9">
+      <c r="A69">
+        <v>2084</v>
+      </c>
+      <c r="B69">
+        <v>1294.23202202283</v>
+      </c>
+      <c r="C69">
+        <v>799.069543476357</v>
+      </c>
+      <c r="D69">
+        <v>331.336619701731</v>
+      </c>
+      <c r="E69">
+        <v>13.3995188800066</v>
+      </c>
+      <c r="F69">
+        <v>47.5073850879936</v>
+      </c>
+      <c r="G69">
+        <v>50.312</v>
+      </c>
+      <c r="I69">
+        <f t="shared" si="2"/>
+        <v>52.6069548767418</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9">
+      <c r="A70">
+        <v>2085</v>
+      </c>
+      <c r="B70">
+        <v>1302.90178719181</v>
+      </c>
+      <c r="C70">
+        <v>805.48704148267</v>
+      </c>
+      <c r="D70">
+        <v>334.465118365963</v>
+      </c>
+      <c r="E70">
+        <v>13.3995188800066</v>
+      </c>
+      <c r="F70">
+        <v>47.5073850879936</v>
+      </c>
+      <c r="G70">
+        <v>50.312</v>
+      </c>
+      <c r="I70">
+        <f t="shared" si="2"/>
+        <v>51.7307233751768</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9">
+      <c r="A71">
+        <v>2086</v>
+      </c>
+      <c r="B71">
+        <v>1311.25455641803</v>
+      </c>
+      <c r="C71">
+        <v>811.777221033917</v>
+      </c>
+      <c r="D71">
+        <v>337.546360568871</v>
+      </c>
+      <c r="E71">
+        <v>13.3995188800066</v>
+      </c>
+      <c r="F71">
+        <v>47.5073850879936</v>
+      </c>
+      <c r="G71">
+        <v>50.312</v>
+      </c>
+      <c r="I71">
+        <f t="shared" si="2"/>
+        <v>50.7120708472417</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9">
+      <c r="A72">
+        <v>2087</v>
+      </c>
+      <c r="B72">
+        <v>1319.29235563165</v>
+      </c>
+      <c r="C72">
+        <v>817.928851169287</v>
+      </c>
+      <c r="D72">
+        <v>340.571609259389</v>
+      </c>
+      <c r="E72">
+        <v>13.3995188800066</v>
+      </c>
+      <c r="F72">
+        <v>47.5073850879936</v>
+      </c>
+      <c r="G72">
+        <v>50.312</v>
+      </c>
+      <c r="I72">
+        <f t="shared" si="2"/>
+        <v>49.5729912349738</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9">
+      <c r="A73">
+        <v>2088</v>
+      </c>
+      <c r="B73">
+        <v>1327.01680405308</v>
+      </c>
+      <c r="C73">
+        <v>823.931531522358</v>
+      </c>
+      <c r="D73">
+        <v>343.533947707684</v>
+      </c>
+      <c r="E73">
+        <v>13.3995188800066</v>
+      </c>
+      <c r="F73">
+        <v>47.5073850879936</v>
+      </c>
+      <c r="G73">
+        <v>50.312</v>
+      </c>
+      <c r="I73">
+        <f t="shared" si="2"/>
+        <v>48.3324208550378</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9">
+      <c r="A74">
+        <v>2089</v>
+      </c>
+      <c r="B74">
+        <v>1334.42918355742</v>
+      </c>
+      <c r="C74">
+        <v>829.776833817269</v>
+      </c>
+      <c r="D74">
+        <v>346.426956523555</v>
+      </c>
+      <c r="E74">
+        <v>13.3995188800066</v>
+      </c>
+      <c r="F74">
+        <v>47.5073850879936</v>
+      </c>
+      <c r="G74">
+        <v>50.312</v>
+      </c>
+      <c r="I74">
+        <f t="shared" si="2"/>
+        <v>47.0064892485957</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9">
+      <c r="A75">
+        <v>2090</v>
+      </c>
+      <c r="B75">
+        <v>1341.53049147956</v>
+      </c>
+      <c r="C75">
+        <v>835.457499012705</v>
+      </c>
+      <c r="D75">
+        <v>349.245167809942</v>
+      </c>
+      <c r="E75">
+        <v>13.3995188800066</v>
+      </c>
+      <c r="F75">
+        <v>47.5073850879936</v>
+      </c>
+      <c r="G75">
+        <v>50.312</v>
+      </c>
+      <c r="I75">
+        <f t="shared" si="2"/>
+        <v>45.6089206889128</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9">
+      <c r="A76">
+        <v>2091</v>
+      </c>
+      <c r="B76">
+        <v>1349.29824383012</v>
+      </c>
+      <c r="C76">
+        <v>840.981869829714</v>
+      </c>
+      <c r="D76">
+        <v>351.991744157062</v>
+      </c>
+      <c r="E76">
+        <v>13.3995188800066</v>
+      </c>
+      <c r="F76">
+        <v>47.5073850879936</v>
+      </c>
+      <c r="G76">
+        <v>50.312</v>
+      </c>
+      <c r="I76">
+        <f t="shared" si="2"/>
+        <v>45.1057258753439</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9">
+      <c r="A77">
+        <v>2092</v>
+      </c>
+      <c r="B77">
+        <v>1356.73121879643</v>
+      </c>
+      <c r="C77">
+        <v>846.419720516434</v>
+      </c>
+      <c r="D77">
+        <v>354.705627171545</v>
+      </c>
+      <c r="E77">
+        <v>13.3995188800066</v>
+      </c>
+      <c r="F77">
+        <v>47.5073850879936</v>
+      </c>
+      <c r="G77">
+        <v>50.312</v>
+      </c>
+      <c r="I77">
+        <f t="shared" si="2"/>
+        <v>44.3869671404508</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9">
+      <c r="A78">
+        <v>2093</v>
+      </c>
+      <c r="B78">
+        <v>1363.83046277701</v>
+      </c>
+      <c r="C78">
+        <v>851.75291811316</v>
+      </c>
+      <c r="D78">
+        <v>357.37464350514</v>
+      </c>
+      <c r="E78">
+        <v>13.3995188800066</v>
+      </c>
+      <c r="F78">
+        <v>47.5073850879936</v>
+      </c>
+      <c r="G78">
+        <v>50.312</v>
+      </c>
+      <c r="I78">
+        <f t="shared" si="2"/>
+        <v>43.4839971907099</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9">
+      <c r="A79">
+        <v>2094</v>
+      </c>
+      <c r="B79">
+        <v>1370.59695598397</v>
+      </c>
+      <c r="C79">
+        <v>856.964148617885</v>
+      </c>
+      <c r="D79">
+        <v>359.988972539539</v>
+      </c>
+      <c r="E79">
+        <v>13.3995188800066</v>
+      </c>
+      <c r="F79">
+        <v>47.5073850879936</v>
+      </c>
+      <c r="G79">
+        <v>50.312</v>
+      </c>
+      <c r="I79">
+        <f t="shared" si="2"/>
+        <v>42.4249308585458</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9">
+      <c r="A80">
+        <v>2095</v>
+      </c>
+      <c r="B80">
+        <v>1377.03170632034</v>
+      </c>
+      <c r="C80">
+        <v>862.039049023897</v>
+      </c>
+      <c r="D80">
+        <v>362.539291137514</v>
+      </c>
+      <c r="E80">
+        <v>13.3995188800066</v>
+      </c>
+      <c r="F80">
+        <v>47.5073850879936</v>
+      </c>
+      <c r="G80">
+        <v>50.312</v>
+      </c>
+      <c r="I80">
+        <f t="shared" si="2"/>
+        <v>41.2344621909288</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9">
+      <c r="A81">
+        <v>2096</v>
+      </c>
+      <c r="B81">
+        <v>1383.13579937114</v>
+      </c>
+      <c r="C81">
+        <v>866.965340269367</v>
+      </c>
+      <c r="D81">
+        <v>365.017690400356</v>
+      </c>
+      <c r="E81">
+        <v>13.3995188800066</v>
+      </c>
+      <c r="F81">
+        <v>47.5073850879936</v>
+      </c>
+      <c r="G81">
+        <v>50.312</v>
+      </c>
+      <c r="I81">
+        <f t="shared" si="2"/>
+        <v>39.9338647334168</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9">
+      <c r="A82">
+        <v>2097</v>
+      </c>
+      <c r="B82">
+        <v>1388.91045771782</v>
+      </c>
+      <c r="C82">
+        <v>871.732792193374</v>
+      </c>
+      <c r="D82">
+        <v>367.417289609064</v>
+      </c>
+      <c r="E82">
+        <v>13.3995188800066</v>
+      </c>
+      <c r="F82">
+        <v>47.5073850879936</v>
+      </c>
+      <c r="G82">
+        <v>50.312</v>
+      </c>
+      <c r="I82">
+        <f t="shared" si="2"/>
+        <v>38.5414719473817</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9">
+      <c r="A83">
+        <v>2098</v>
+      </c>
+      <c r="B83">
+        <v>1394.3570903982</v>
+      </c>
+      <c r="C83">
+        <v>876.33290167514</v>
+      </c>
+      <c r="D83">
+        <v>369.732233682434</v>
+      </c>
+      <c r="E83">
+        <v>13.3995188800066</v>
+      </c>
+      <c r="F83">
+        <v>47.5073850879936</v>
+      </c>
+      <c r="G83">
+        <v>50.312</v>
+      </c>
+      <c r="I83">
+        <f t="shared" si="2"/>
+        <v>37.0730510726258</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9">
+      <c r="A84">
+        <v>2099</v>
+      </c>
+      <c r="B84">
+        <v>1399.47733802155</v>
+      </c>
+      <c r="C84">
+        <v>880.758685793611</v>
+      </c>
+      <c r="D84">
+        <v>371.957548431524</v>
+      </c>
+      <c r="E84">
+        <v>13.3995188800066</v>
+      </c>
+      <c r="F84">
+        <v>47.5073850879936</v>
+      </c>
+      <c r="G84">
+        <v>50.312</v>
+      </c>
+      <c r="I84">
+        <f t="shared" si="2"/>
+        <v>35.5421998284147</v>
+      </c>
+    </row>
+    <row r="85" spans="2:2">
+      <c r="B85">
+        <v>1404.27311073691</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>